--- a/inst/extdata/template_custom_result_format.xlsx
+++ b/inst/extdata/template_custom_result_format.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nbep.sharepoint.com/sites/ARCGIS/Shared Documents/GIS_PROJECTS/INTERNAL_PROJECTS/MassWateR/MassWateRdash/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="65" documentId="8_{47F3C27D-FFF2-4B59-AAED-0D5C0D6C01AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21B1DB53-B5A3-4423-A434-8878AE5F9C61}"/>
+  <xr:revisionPtr revIDLastSave="70" documentId="8_{47F3C27D-FFF2-4B59-AAED-0D5C0D6C01AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A03D0B3-8AAB-4F6B-9E13-B84745D1BD4B}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{15A63773-4D10-4721-8873-E00384479068}"/>
+    <workbookView xWindow="-28920" yWindow="630" windowWidth="29040" windowHeight="15720" xr2:uid="{15A63773-4D10-4721-8873-E00384479068}"/>
   </bookViews>
   <sheets>
     <sheet name="Column Names" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="146">
   <si>
     <t>MassWateR</t>
   </si>
@@ -476,6 +476,12 @@
   </si>
   <si>
     <t>Questionable</t>
+  </si>
+  <si>
+    <t>Quantitation Limit Unit</t>
+  </si>
+  <si>
+    <t>Optional. Unit used for Quantitation Limit. If this column is left blank, Result Unit is used instead.</t>
   </si>
 </sst>
 </file>
@@ -561,7 +567,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -577,6 +583,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -893,10 +902,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B1AF79F-D8EC-4E16-A1DF-F24CF46E8F72}">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="40.77734375" customWidth="1"/>
     <col min="3" max="3" width="90.77734375" style="2" customWidth="1"/>
   </cols>
@@ -1072,6 +1081,15 @@
       <c r="B19" s="3"/>
       <c r="C19" s="7" t="s">
         <v>138</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="8" t="s">
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -1808,12 +1826,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="361498ed-2f37-4a7b-aa85-b7e3bb12cf14">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="86c687f1-a147-44ae-bd23-8fe29c8c5955" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2038,20 +2058,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="361498ed-2f37-4a7b-aa85-b7e3bb12cf14">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="86c687f1-a147-44ae-bd23-8fe29c8c5955" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C768B5AF-0087-4601-966E-E7B2F56E1083}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3803D693-7268-473F-859D-789A63ACD111}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="361498ed-2f37-4a7b-aa85-b7e3bb12cf14"/>
+    <ds:schemaRef ds:uri="86c687f1-a147-44ae-bd23-8fe29c8c5955"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2076,12 +2097,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3803D693-7268-473F-859D-789A63ACD111}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C768B5AF-0087-4601-966E-E7B2F56E1083}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="361498ed-2f37-4a7b-aa85-b7e3bb12cf14"/>
-    <ds:schemaRef ds:uri="86c687f1-a147-44ae-bd23-8fe29c8c5955"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>